--- a/public/templates/agent-import-template.xlsx
+++ b/public/templates/agent-import-template.xlsx
@@ -397,109 +397,297 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:I3"/>
+  <dimension ref="A1:AN2"/>
   <cols>
-    <col min="1" max="1" width="15.83203125" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
-    <col min="3" max="3" width="30.83203125" customWidth="1"/>
-    <col min="4" max="4" width="15.83203125" customWidth="1"/>
-    <col min="5" max="5" width="15.83203125" customWidth="1"/>
-    <col min="6" max="6" width="20.83203125" customWidth="1"/>
-    <col min="7" max="7" width="25.83203125" customWidth="1"/>
-    <col min="8" max="8" width="30.83203125" customWidth="1"/>
-    <col min="9" max="9" width="10.83203125" customWidth="1"/>
+    <col min="1" max="1" width="18.83203125" customWidth="1"/>
+    <col min="2" max="2" width="18.83203125" customWidth="1"/>
+    <col min="3" max="3" width="18.83203125" customWidth="1"/>
+    <col min="4" max="4" width="18.83203125" customWidth="1"/>
+    <col min="5" max="5" width="18.83203125" customWidth="1"/>
+    <col min="6" max="6" width="18.83203125" customWidth="1"/>
+    <col min="7" max="7" width="18.83203125" customWidth="1"/>
+    <col min="8" max="8" width="18.83203125" customWidth="1"/>
+    <col min="9" max="9" width="18.83203125" customWidth="1"/>
+    <col min="10" max="10" width="18.83203125" customWidth="1"/>
+    <col min="11" max="11" width="18.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.83203125" customWidth="1"/>
+    <col min="13" max="13" width="18.83203125" customWidth="1"/>
+    <col min="14" max="14" width="19.83203125" customWidth="1"/>
+    <col min="15" max="15" width="20.83203125" customWidth="1"/>
+    <col min="16" max="16" width="18.83203125" customWidth="1"/>
+    <col min="17" max="17" width="18.83203125" customWidth="1"/>
+    <col min="18" max="18" width="18.83203125" customWidth="1"/>
+    <col min="19" max="19" width="18.83203125" customWidth="1"/>
+    <col min="20" max="20" width="18.83203125" customWidth="1"/>
+    <col min="21" max="21" width="18.83203125" customWidth="1"/>
+    <col min="22" max="22" width="18.83203125" customWidth="1"/>
+    <col min="23" max="23" width="18.83203125" customWidth="1"/>
+    <col min="24" max="24" width="18.83203125" customWidth="1"/>
+    <col min="25" max="25" width="18.83203125" customWidth="1"/>
+    <col min="26" max="26" width="18.83203125" customWidth="1"/>
+    <col min="27" max="27" width="18.83203125" customWidth="1"/>
+    <col min="28" max="28" width="18.83203125" customWidth="1"/>
+    <col min="29" max="29" width="18.83203125" customWidth="1"/>
+    <col min="30" max="30" width="18.83203125" customWidth="1"/>
+    <col min="31" max="31" width="18.83203125" customWidth="1"/>
+    <col min="32" max="32" width="18.83203125" customWidth="1"/>
+    <col min="33" max="33" width="18.83203125" customWidth="1"/>
+    <col min="34" max="34" width="18.83203125" customWidth="1"/>
+    <col min="35" max="35" width="18.83203125" customWidth="1"/>
+    <col min="36" max="36" width="18.83203125" customWidth="1"/>
+    <col min="37" max="37" width="18.83203125" customWidth="1"/>
+    <col min="38" max="38" width="18.83203125" customWidth="1"/>
+    <col min="39" max="39" width="18.83203125" customWidth="1"/>
+    <col min="40" max="40" width="18.83203125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
+        <v>Agent ID</v>
+      </c>
+      <c r="B1" t="str">
+        <v>Role</v>
+      </c>
+      <c r="C1" t="str">
         <v>First Name</v>
       </c>
-      <c r="B1" t="str">
+      <c r="D1" t="str">
         <v>Last Name</v>
       </c>
-      <c r="C1" t="str">
+      <c r="E1" t="str">
         <v>Email</v>
       </c>
-      <c r="D1" t="str">
+      <c r="F1" t="str">
+        <v>Personal Email</v>
+      </c>
+      <c r="G1" t="str">
+        <v>Phone</v>
+      </c>
+      <c r="H1" t="str">
         <v>Mobile Phone</v>
       </c>
-      <c r="E1" t="str">
+      <c r="I1" t="str">
         <v>Office Phone</v>
       </c>
-      <c r="F1" t="str">
+      <c r="J1" t="str">
+        <v>Website</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Company</v>
+      </c>
+      <c r="L1" t="str">
+        <v>Job Title</v>
+      </c>
+      <c r="M1" t="str">
         <v>Position</v>
       </c>
-      <c r="G1" t="str">
-        <v>Company</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Website</v>
-      </c>
-      <c r="I1" t="str">
+      <c r="N1" t="str">
+        <v>Assigned Member</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Assigned Company</v>
+      </c>
+      <c r="P1" t="str">
+        <v>Visibility</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Contact Type</v>
+      </c>
+      <c r="R1" t="str">
+        <v>Lead Source</v>
+      </c>
+      <c r="S1" t="str">
+        <v>Lead Status</v>
+      </c>
+      <c r="T1" t="str">
+        <v>Lead Type</v>
+      </c>
+      <c r="U1" t="str">
+        <v>Referred By</v>
+      </c>
+      <c r="V1" t="str">
+        <v>Campaign</v>
+      </c>
+      <c r="W1" t="str">
         <v>Status</v>
+      </c>
+      <c r="X1" t="str">
+        <v>Birthday</v>
+      </c>
+      <c r="Y1" t="str">
+        <v>Address Line 1</v>
+      </c>
+      <c r="Z1" t="str">
+        <v>Address Line 2</v>
+      </c>
+      <c r="AA1" t="str">
+        <v>Address</v>
+      </c>
+      <c r="AB1" t="str">
+        <v>City</v>
+      </c>
+      <c r="AC1" t="str">
+        <v>State</v>
+      </c>
+      <c r="AD1" t="str">
+        <v>Country</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>Postal Code</v>
+      </c>
+      <c r="AF1" t="str">
+        <v>Description</v>
+      </c>
+      <c r="AG1" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="AH1" t="str">
+        <v>Twitter</v>
+      </c>
+      <c r="AI1" t="str">
+        <v>Facebook</v>
+      </c>
+      <c r="AJ1" t="str">
+        <v>LinkedIn</v>
+      </c>
+      <c r="AK1" t="str">
+        <v>Thread</v>
+      </c>
+      <c r="AL1" t="str">
+        <v>Instagram</v>
+      </c>
+      <c r="AM1" t="str">
+        <v>YouTube</v>
+      </c>
+      <c r="AN1" t="str">
+        <v>TikTok</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
+        <v>AGT-001</v>
+      </c>
+      <c r="B2" t="str">
+        <v>Agent</v>
+      </c>
+      <c r="C2" t="str">
         <v>John</v>
       </c>
-      <c r="B2" t="str">
+      <c r="D2" t="str">
         <v>Doe</v>
       </c>
-      <c r="C2" t="str">
+      <c r="E2" t="str">
         <v>john.doe@example.com</v>
       </c>
-      <c r="D2" t="str">
-        <v>+1234567890</v>
-      </c>
-      <c r="E2" t="str">
-        <v>+1234567891</v>
-      </c>
       <c r="F2" t="str">
+        <v>john.personal@example.com</v>
+      </c>
+      <c r="G2" t="str">
+        <v>+12345678900</v>
+      </c>
+      <c r="H2" t="str">
+        <v>+12345678901</v>
+      </c>
+      <c r="I2" t="str">
+        <v>+12345678902</v>
+      </c>
+      <c r="J2" t="str">
+        <v>https://example.com</v>
+      </c>
+      <c r="K2" t="str">
+        <v>ABC Insurance</v>
+      </c>
+      <c r="L2" t="str">
+        <v>Senior Agent</v>
+      </c>
+      <c r="M2" t="str">
         <v>Insurance Agent</v>
       </c>
-      <c r="G2" t="str">
-        <v>ABC Insurance</v>
-      </c>
-      <c r="H2" t="str">
-        <v>https://example.com</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Active</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="str">
-        <v>Jane</v>
-      </c>
-      <c r="B3" t="str">
-        <v>Smith</v>
-      </c>
-      <c r="C3" t="str">
-        <v>jane.smith@example.com</v>
-      </c>
-      <c r="D3" t="str">
-        <v>+1234567892</v>
-      </c>
-      <c r="E3" t="str">
-        <v>+1234567893</v>
-      </c>
-      <c r="F3" t="str">
-        <v>Senior Agent</v>
-      </c>
-      <c r="G3" t="str">
-        <v>XYZ Brokers</v>
-      </c>
-      <c r="H3" t="str">
-        <v>https://xyzbrokers.com</v>
-      </c>
-      <c r="I3" t="str">
-        <v>Active</v>
+      <c r="N2" t="str">
+        <v/>
+      </c>
+      <c r="O2" t="str">
+        <v/>
+      </c>
+      <c r="P2" t="str">
+        <v>all_members</v>
+      </c>
+      <c r="Q2" t="str">
+        <v/>
+      </c>
+      <c r="R2" t="str">
+        <v/>
+      </c>
+      <c r="S2" t="str">
+        <v/>
+      </c>
+      <c r="T2" t="str">
+        <v/>
+      </c>
+      <c r="U2" t="str">
+        <v/>
+      </c>
+      <c r="V2" t="str">
+        <v/>
+      </c>
+      <c r="W2" t="str">
+        <v>active</v>
+      </c>
+      <c r="X2" t="str">
+        <v>1985-06-15</v>
+      </c>
+      <c r="Y2" t="str">
+        <v>123 Main St</v>
+      </c>
+      <c r="Z2" t="str">
+        <v>Suite 100</v>
+      </c>
+      <c r="AA2" t="str">
+        <v>123 Main St, Suite 100</v>
+      </c>
+      <c r="AB2" t="str">
+        <v>New York</v>
+      </c>
+      <c r="AC2" t="str">
+        <v>NY</v>
+      </c>
+      <c r="AD2" t="str">
+        <v>United States</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>10001</v>
+      </c>
+      <c r="AF2" t="str">
+        <v>Experienced insurance agent</v>
+      </c>
+      <c r="AG2" t="str">
+        <v>Internal notes here</v>
+      </c>
+      <c r="AH2" t="str">
+        <v>https://twitter.com/johndoe</v>
+      </c>
+      <c r="AI2" t="str">
+        <v>https://facebook.com/johndoe</v>
+      </c>
+      <c r="AJ2" t="str">
+        <v>https://linkedin.com/in/johndoe</v>
+      </c>
+      <c r="AK2" t="str">
+        <v>johndoe</v>
+      </c>
+      <c r="AL2" t="str">
+        <v>https://instagram.com/johndoe</v>
+      </c>
+      <c r="AM2" t="str">
+        <v>https://youtube.com/@johndoe</v>
+      </c>
+      <c r="AN2" t="str">
+        <v>https://tiktok.com/@johndoe</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:I3"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AN2"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/templates/agent-import-template.xlsx
+++ b/public/templates/agent-import-template.xlsx
@@ -397,107 +397,65 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:AN2"/>
-  <cols>
-    <col min="1" max="1" width="18.83203125" customWidth="1"/>
-    <col min="2" max="2" width="18.83203125" customWidth="1"/>
-    <col min="3" max="3" width="18.83203125" customWidth="1"/>
-    <col min="4" max="4" width="18.83203125" customWidth="1"/>
-    <col min="5" max="5" width="18.83203125" customWidth="1"/>
-    <col min="6" max="6" width="18.83203125" customWidth="1"/>
-    <col min="7" max="7" width="18.83203125" customWidth="1"/>
-    <col min="8" max="8" width="18.83203125" customWidth="1"/>
-    <col min="9" max="9" width="18.83203125" customWidth="1"/>
-    <col min="10" max="10" width="18.83203125" customWidth="1"/>
-    <col min="11" max="11" width="18.83203125" customWidth="1"/>
-    <col min="12" max="12" width="18.83203125" customWidth="1"/>
-    <col min="13" max="13" width="18.83203125" customWidth="1"/>
-    <col min="14" max="14" width="19.83203125" customWidth="1"/>
-    <col min="15" max="15" width="20.83203125" customWidth="1"/>
-    <col min="16" max="16" width="18.83203125" customWidth="1"/>
-    <col min="17" max="17" width="18.83203125" customWidth="1"/>
-    <col min="18" max="18" width="18.83203125" customWidth="1"/>
-    <col min="19" max="19" width="18.83203125" customWidth="1"/>
-    <col min="20" max="20" width="18.83203125" customWidth="1"/>
-    <col min="21" max="21" width="18.83203125" customWidth="1"/>
-    <col min="22" max="22" width="18.83203125" customWidth="1"/>
-    <col min="23" max="23" width="18.83203125" customWidth="1"/>
-    <col min="24" max="24" width="18.83203125" customWidth="1"/>
-    <col min="25" max="25" width="18.83203125" customWidth="1"/>
-    <col min="26" max="26" width="18.83203125" customWidth="1"/>
-    <col min="27" max="27" width="18.83203125" customWidth="1"/>
-    <col min="28" max="28" width="18.83203125" customWidth="1"/>
-    <col min="29" max="29" width="18.83203125" customWidth="1"/>
-    <col min="30" max="30" width="18.83203125" customWidth="1"/>
-    <col min="31" max="31" width="18.83203125" customWidth="1"/>
-    <col min="32" max="32" width="18.83203125" customWidth="1"/>
-    <col min="33" max="33" width="18.83203125" customWidth="1"/>
-    <col min="34" max="34" width="18.83203125" customWidth="1"/>
-    <col min="35" max="35" width="18.83203125" customWidth="1"/>
-    <col min="36" max="36" width="18.83203125" customWidth="1"/>
-    <col min="37" max="37" width="18.83203125" customWidth="1"/>
-    <col min="38" max="38" width="18.83203125" customWidth="1"/>
-    <col min="39" max="39" width="18.83203125" customWidth="1"/>
-    <col min="40" max="40" width="18.83203125" customWidth="1"/>
-  </cols>
+  <dimension ref="A1:AF2"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
-        <v>Agent ID</v>
+        <v>Agent Photo</v>
       </c>
       <c r="B1" t="str">
-        <v>Role</v>
+        <v>FirstName</v>
       </c>
       <c r="C1" t="str">
-        <v>First Name</v>
+        <v>LastName</v>
       </c>
       <c r="D1" t="str">
-        <v>Last Name</v>
+        <v>City</v>
       </c>
       <c r="E1" t="str">
+        <v>State</v>
+      </c>
+      <c r="F1" t="str">
+        <v>Zipcode</v>
+      </c>
+      <c r="G1" t="str">
+        <v>CellPhone</v>
+      </c>
+      <c r="H1" t="str">
         <v>Email</v>
       </c>
-      <c r="F1" t="str">
-        <v>Personal Email</v>
-      </c>
-      <c r="G1" t="str">
-        <v>Phone</v>
-      </c>
-      <c r="H1" t="str">
-        <v>Mobile Phone</v>
-      </c>
       <c r="I1" t="str">
-        <v>Office Phone</v>
+        <v>AgentNumber</v>
       </c>
       <c r="J1" t="str">
+        <v>AgentStatus</v>
+      </c>
+      <c r="K1" t="str">
+        <v>Date Recruited</v>
+      </c>
+      <c r="L1" t="str">
+        <v>AgentLevel</v>
+      </c>
+      <c r="M1" t="str">
+        <v>Address</v>
+      </c>
+      <c r="N1" t="str">
+        <v>Recruiter Name</v>
+      </c>
+      <c r="O1" t="str">
+        <v>Date of Birth</v>
+      </c>
+      <c r="P1" t="str">
+        <v>ASSIGNED TO</v>
+      </c>
+      <c r="Q1" t="str">
+        <v>Visibility</v>
+      </c>
+      <c r="R1" t="str">
         <v>Website</v>
       </c>
-      <c r="K1" t="str">
-        <v>Company</v>
-      </c>
-      <c r="L1" t="str">
-        <v>Job Title</v>
-      </c>
-      <c r="M1" t="str">
-        <v>Position</v>
-      </c>
-      <c r="N1" t="str">
-        <v>Assigned Member</v>
-      </c>
-      <c r="O1" t="str">
-        <v>Assigned Company</v>
-      </c>
-      <c r="P1" t="str">
-        <v>Visibility</v>
-      </c>
-      <c r="Q1" t="str">
-        <v>Contact Type</v>
-      </c>
-      <c r="R1" t="str">
+      <c r="S1" t="str">
         <v>Lead Source</v>
-      </c>
-      <c r="S1" t="str">
-        <v>Lead Status</v>
       </c>
       <c r="T1" t="str">
         <v>Lead Type</v>
@@ -509,185 +467,137 @@
         <v>Campaign</v>
       </c>
       <c r="W1" t="str">
-        <v>Status</v>
+        <v>Twitter</v>
       </c>
       <c r="X1" t="str">
-        <v>Birthday</v>
+        <v>Facebook</v>
       </c>
       <c r="Y1" t="str">
-        <v>Address Line 1</v>
+        <v>LinkedIn</v>
       </c>
       <c r="Z1" t="str">
-        <v>Address Line 2</v>
+        <v>Thread</v>
       </c>
       <c r="AA1" t="str">
-        <v>Address</v>
+        <v>Instagram</v>
       </c>
       <c r="AB1" t="str">
-        <v>City</v>
+        <v>YouTube</v>
       </c>
       <c r="AC1" t="str">
-        <v>State</v>
+        <v>TikTok</v>
       </c>
       <c r="AD1" t="str">
+        <v>Notes</v>
+      </c>
+      <c r="AE1" t="str">
+        <v>Assigned Company</v>
+      </c>
+      <c r="AF1" t="str">
         <v>Country</v>
-      </c>
-      <c r="AE1" t="str">
-        <v>Postal Code</v>
-      </c>
-      <c r="AF1" t="str">
-        <v>Description</v>
-      </c>
-      <c r="AG1" t="str">
-        <v>Notes</v>
-      </c>
-      <c r="AH1" t="str">
-        <v>Twitter</v>
-      </c>
-      <c r="AI1" t="str">
-        <v>Facebook</v>
-      </c>
-      <c r="AJ1" t="str">
-        <v>LinkedIn</v>
-      </c>
-      <c r="AK1" t="str">
-        <v>Thread</v>
-      </c>
-      <c r="AL1" t="str">
-        <v>Instagram</v>
-      </c>
-      <c r="AM1" t="str">
-        <v>YouTube</v>
-      </c>
-      <c r="AN1" t="str">
-        <v>TikTok</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="str">
-        <v>AGT-001</v>
+        <v/>
       </c>
       <c r="B2" t="str">
-        <v>Agent</v>
+        <v>Sophia</v>
       </c>
       <c r="C2" t="str">
-        <v>John</v>
+        <v>Anderson</v>
       </c>
       <c r="D2" t="str">
-        <v>Doe</v>
+        <v>New York</v>
       </c>
       <c r="E2" t="str">
-        <v>john.doe@example.com</v>
+        <v>NY</v>
       </c>
       <c r="F2" t="str">
-        <v>john.personal@example.com</v>
+        <v>10001</v>
       </c>
       <c r="G2" t="str">
-        <v>+12345678900</v>
+        <v>+1-212-555-0199</v>
       </c>
       <c r="H2" t="str">
-        <v>+12345678901</v>
+        <v>sophia.anderson@example.com</v>
       </c>
       <c r="I2" t="str">
-        <v>+12345678902</v>
+        <v>NAA550001</v>
       </c>
       <c r="J2" t="str">
-        <v>https://example.com</v>
+        <v>Active</v>
       </c>
       <c r="K2" t="str">
-        <v>ABC Insurance</v>
+        <v>2026-07-15</v>
       </c>
       <c r="L2" t="str">
-        <v>Senior Agent</v>
+        <v>55</v>
       </c>
       <c r="M2" t="str">
-        <v>Insurance Agent</v>
+        <v>125 Madison Avenue</v>
       </c>
       <c r="N2" t="str">
-        <v/>
+        <v>John Carter</v>
       </c>
       <c r="O2" t="str">
-        <v/>
+        <v>1990-05-20</v>
       </c>
       <c r="P2" t="str">
-        <v>all_members</v>
+        <v>Manager A</v>
       </c>
       <c r="Q2" t="str">
-        <v/>
+        <v>Public</v>
       </c>
       <c r="R2" t="str">
-        <v/>
+        <v>https://www.example.com/agents/sophia-anderson</v>
       </c>
       <c r="S2" t="str">
-        <v/>
+        <v>LinkedIn</v>
       </c>
       <c r="T2" t="str">
-        <v/>
+        <v>Inbound</v>
       </c>
       <c r="U2" t="str">
-        <v/>
+        <v>Global Realty Partner</v>
       </c>
       <c r="V2" t="str">
-        <v/>
+        <v>US Real Estate Campaign 1</v>
       </c>
       <c r="W2" t="str">
-        <v>active</v>
+        <v>https://twitter.com/sophiaanderson</v>
       </c>
       <c r="X2" t="str">
-        <v>1985-06-15</v>
+        <v>https://facebook.com/sophia.anderson</v>
       </c>
       <c r="Y2" t="str">
-        <v>123 Main St</v>
+        <v>https://linkedin.com/in/sophia-anderson</v>
       </c>
       <c r="Z2" t="str">
-        <v>Suite 100</v>
+        <v>https://threads.net/@sophiaanderson</v>
       </c>
       <c r="AA2" t="str">
-        <v>123 Main St, Suite 100</v>
+        <v>https://instagram.com/sophiaanderson</v>
       </c>
       <c r="AB2" t="str">
-        <v>New York</v>
+        <v>https://youtube.com/@sophiaanderson</v>
       </c>
       <c r="AC2" t="str">
-        <v>NY</v>
+        <v>https://tiktok.com/@sophiaanderson</v>
       </c>
       <c r="AD2" t="str">
+        <v>Dummy foreign client record for import testing.</v>
+      </c>
+      <c r="AE2" t="str">
+        <v>NorthStar Realty</v>
+      </c>
+      <c r="AF2" t="str">
         <v>United States</v>
-      </c>
-      <c r="AE2" t="str">
-        <v>10001</v>
-      </c>
-      <c r="AF2" t="str">
-        <v>Experienced insurance agent</v>
-      </c>
-      <c r="AG2" t="str">
-        <v>Internal notes here</v>
-      </c>
-      <c r="AH2" t="str">
-        <v>https://twitter.com/johndoe</v>
-      </c>
-      <c r="AI2" t="str">
-        <v>https://facebook.com/johndoe</v>
-      </c>
-      <c r="AJ2" t="str">
-        <v>https://linkedin.com/in/johndoe</v>
-      </c>
-      <c r="AK2" t="str">
-        <v>johndoe</v>
-      </c>
-      <c r="AL2" t="str">
-        <v>https://instagram.com/johndoe</v>
-      </c>
-      <c r="AM2" t="str">
-        <v>https://youtube.com/@johndoe</v>
-      </c>
-      <c r="AN2" t="str">
-        <v>https://tiktok.com/@johndoe</v>
       </c>
     </row>
   </sheetData>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:AN2"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:AF2"/>
   </ignoredErrors>
 </worksheet>
 </file>